--- a/Zinc/5. Cluster analysis/Clustering by sample results/Sites_by_network_typology.xlsx
+++ b/Zinc/5. Cluster analysis/Clustering by sample results/Sites_by_network_typology.xlsx
@@ -1,319 +1,326 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://irtacat-my.sharepoint.com/personal/cecilia_albert_irta_cat/Documents/Escriptori/Trace-element-bioavailability-spatial-assessment/Zinc/5. Cluster analysis/Clustering by sample results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_B892312730C927BD06C731FA5F3D01118A9B7B5F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8439AFD-6649-49E7-AC0F-F8CC61D4C5BD}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
-  <si>
-    <t xml:space="preserve">Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Typologies_Observed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominant_Typology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Perennial (n=4); Pooled (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Perennial (n=4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NBO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NBO3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Perennial (n=4); Perennial (n=2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL5.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial (n=3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial (n=5); Developed Perennial (n=3); Pooled (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial (n=8); Developed Perennial (n=3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial (n=5); Developed Perennial (n=5); Non-Perennial (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NBO5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial (n=4); Pooled (n=2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S_TRIB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gum Hollow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial (n=11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mill Branch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinhook Branch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial (n=9); Main Stem (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WBK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WBK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial (n=2); Pooled (n=2); Non-Perennial (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WBK3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial (n=7); Pooled (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial (n=8); Main Stem (n=3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial (n=9); Perennial (n=1); Main Stem (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial (n=10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial (n=8); Perennial (n=1); Main Stem (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial (n=9); Perennial (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial (n=10); Perennial (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial (n=10); Main Stem (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial (n=9); Main Stem (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Downtown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial (n=5); Main Stem (n=3); Perennial (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial (n=8); Perennial (n=3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NBO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial (n=8); Main Stem (n=2); Perennial (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WBK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial (n=11); Perennial (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem (n=11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK10.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem (n=10); Perennial (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK11.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK13.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem (n=9); Perennial (n=2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK16.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK18.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem (n=9); Perennial (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK2.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK23.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK5.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK7.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem (n=8); Perennial (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCK0.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem (n=6); Developed Perennial (n=4); Perennial (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL4.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pooled (n=5); Perennial (n=2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pooled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL4.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pooled (n=3); Perennial (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL4.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pooled (n=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTN1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pooled (n=8); Developed Perennial (n=2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pooled (n=2)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="98">
+  <si>
+    <t>Network</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Typologies_Observed</t>
+  </si>
+  <si>
+    <t>Dominant_Typology</t>
+  </si>
+  <si>
+    <t>MCA</t>
+  </si>
+  <si>
+    <t>MCA3.2</t>
+  </si>
+  <si>
+    <t>Non-Perennial (n=4); Pooled (n=1)</t>
+  </si>
+  <si>
+    <t>Non-Perennial</t>
+  </si>
+  <si>
+    <t>MCA3.3</t>
+  </si>
+  <si>
+    <t>Non-Perennial (n=4)</t>
+  </si>
+  <si>
+    <t>NBO</t>
+  </si>
+  <si>
+    <t>NBO3</t>
+  </si>
+  <si>
+    <t>Non-Perennial (n=4); Perennial (n=2)</t>
+  </si>
+  <si>
+    <t>BSL</t>
+  </si>
+  <si>
+    <t>BSL5.1</t>
+  </si>
+  <si>
+    <t>Perennial (n=1)</t>
+  </si>
+  <si>
+    <t>Perennial</t>
+  </si>
+  <si>
+    <t>BSL8</t>
+  </si>
+  <si>
+    <t>MCA2</t>
+  </si>
+  <si>
+    <t>Perennial (n=3)</t>
+  </si>
+  <si>
+    <t>MCA3.1</t>
+  </si>
+  <si>
+    <t>Perennial (n=5); Developed Perennial (n=3); Pooled (n=1)</t>
+  </si>
+  <si>
+    <t>MCA4</t>
+  </si>
+  <si>
+    <t>Perennial (n=8); Developed Perennial (n=3)</t>
+  </si>
+  <si>
+    <t>MTN</t>
+  </si>
+  <si>
+    <t>MTN4</t>
+  </si>
+  <si>
+    <t>Perennial (n=5); Developed Perennial (n=5); Non-Perennial (n=1)</t>
+  </si>
+  <si>
+    <t>NBO5</t>
+  </si>
+  <si>
+    <t>Perennial (n=4); Pooled (n=2)</t>
+  </si>
+  <si>
+    <t>S_TRIB</t>
+  </si>
+  <si>
+    <t>Gum Hollow</t>
+  </si>
+  <si>
+    <t>Perennial (n=11)</t>
+  </si>
+  <si>
+    <t>Mill Branch</t>
+  </si>
+  <si>
+    <t>Pinhook Branch</t>
+  </si>
+  <si>
+    <t>Perennial (n=9); Main Stem (n=1)</t>
+  </si>
+  <si>
+    <t>WBK</t>
+  </si>
+  <si>
+    <t>WBK2</t>
+  </si>
+  <si>
+    <t>Perennial (n=2); Pooled (n=2); Non-Perennial (n=1)</t>
+  </si>
+  <si>
+    <t>WBK3</t>
+  </si>
+  <si>
+    <t>Perennial (n=7); Pooled (n=1)</t>
+  </si>
+  <si>
+    <t>BSL1.1</t>
+  </si>
+  <si>
+    <t>Developed Perennial (n=8); Main Stem (n=3)</t>
+  </si>
+  <si>
+    <t>Developed Perennial</t>
+  </si>
+  <si>
+    <t>BSL1.3</t>
+  </si>
+  <si>
+    <t>Developed Perennial (n=9); Perennial (n=1); Main Stem (n=1)</t>
+  </si>
+  <si>
+    <t>BSL2.1</t>
+  </si>
+  <si>
+    <t>Developed Perennial (n=10)</t>
+  </si>
+  <si>
+    <t>BSL2.2</t>
+  </si>
+  <si>
+    <t>Developed Perennial (n=8); Perennial (n=1); Main Stem (n=1)</t>
+  </si>
+  <si>
+    <t>BSL2.3</t>
+  </si>
+  <si>
+    <t>Developed Perennial (n=9); Perennial (n=1)</t>
+  </si>
+  <si>
+    <t>BSL3.1</t>
+  </si>
+  <si>
+    <t>Developed Perennial (n=10); Perennial (n=1)</t>
+  </si>
+  <si>
+    <t>BSL3.2</t>
+  </si>
+  <si>
+    <t>Developed Perennial (n=10); Main Stem (n=1)</t>
+  </si>
+  <si>
+    <t>BSL3.3</t>
+  </si>
+  <si>
+    <t>Developed Perennial (n=9); Main Stem (n=1)</t>
+  </si>
+  <si>
+    <t>Downtown</t>
+  </si>
+  <si>
+    <t>Developed Perennial (n=5); Main Stem (n=3); Perennial (n=1)</t>
+  </si>
+  <si>
+    <t>MCA1</t>
+  </si>
+  <si>
+    <t>Developed Perennial (n=8); Perennial (n=3)</t>
+  </si>
+  <si>
+    <t>NBO2</t>
+  </si>
+  <si>
+    <t>Developed Perennial (n=8); Main Stem (n=2); Perennial (n=1)</t>
+  </si>
+  <si>
+    <t>WBK1</t>
+  </si>
+  <si>
+    <t>Developed Perennial (n=11); Perennial (n=1)</t>
+  </si>
+  <si>
+    <t>BSL1.2</t>
+  </si>
+  <si>
+    <t>Main Stem (n=11)</t>
+  </si>
+  <si>
+    <t>Main Stem</t>
+  </si>
+  <si>
+    <t>EFK</t>
+  </si>
+  <si>
+    <t>EFK10.0</t>
+  </si>
+  <si>
+    <t>Main Stem (n=10); Perennial (n=1)</t>
+  </si>
+  <si>
+    <t>EFK11.3</t>
+  </si>
+  <si>
+    <t>EFK13.8</t>
+  </si>
+  <si>
+    <t>Main Stem (n=9); Perennial (n=2)</t>
+  </si>
+  <si>
+    <t>EFK16.2</t>
+  </si>
+  <si>
+    <t>EFK18.2</t>
+  </si>
+  <si>
+    <t>Main Stem (n=9); Perennial (n=1)</t>
+  </si>
+  <si>
+    <t>EFK2.0</t>
+  </si>
+  <si>
+    <t>EFK20</t>
+  </si>
+  <si>
+    <t>EFK23.5</t>
+  </si>
+  <si>
+    <t>EFK5.4</t>
+  </si>
+  <si>
+    <t>EFK7.9</t>
+  </si>
+  <si>
+    <t>Main Stem (n=8); Perennial (n=1)</t>
+  </si>
+  <si>
+    <t>BCK0.9</t>
+  </si>
+  <si>
+    <t>Main Stem (n=6); Developed Perennial (n=4); Perennial (n=1)</t>
+  </si>
+  <si>
+    <t>BSL4.1</t>
+  </si>
+  <si>
+    <t>Pooled (n=5); Perennial (n=2)</t>
+  </si>
+  <si>
+    <t>Pooled</t>
+  </si>
+  <si>
+    <t>BSL4.2</t>
+  </si>
+  <si>
+    <t>Pooled (n=3); Perennial (n=1)</t>
+  </si>
+  <si>
+    <t>BSL4.3</t>
+  </si>
+  <si>
+    <t>BSL6</t>
+  </si>
+  <si>
+    <t>Pooled (n=1)</t>
+  </si>
+  <si>
+    <t>BSL7</t>
+  </si>
+  <si>
+    <t>MTN1.1</t>
+  </si>
+  <si>
+    <t>Pooled (n=8); Developed Perennial (n=2)</t>
+  </si>
+  <si>
+    <t>MTN2</t>
+  </si>
+  <si>
+    <t>Pooled (n=2)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -349,6 +356,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -630,11 +646,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="54.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -648,7 +668,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -662,7 +682,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -676,7 +696,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -690,7 +710,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -704,7 +724,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -718,7 +738,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -732,7 +752,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -746,7 +766,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -760,7 +780,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -774,7 +794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -788,7 +808,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -802,7 +822,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -816,7 +836,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -830,7 +850,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -844,7 +864,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -858,7 +878,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -872,7 +892,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -886,7 +906,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -900,7 +920,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -914,7 +934,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -928,7 +948,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>13</v>
       </c>
@@ -942,7 +962,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -956,7 +976,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>13</v>
       </c>
@@ -970,7 +990,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -984,7 +1004,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -998,7 +1018,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -1012,7 +1032,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -1026,7 +1046,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -1040,7 +1060,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -1054,7 +1074,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -1068,7 +1088,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -1082,7 +1102,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -1096,7 +1116,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>68</v>
       </c>
@@ -1110,7 +1130,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -1124,7 +1144,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>68</v>
       </c>
@@ -1138,7 +1158,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>68</v>
       </c>
@@ -1152,7 +1172,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>68</v>
       </c>
@@ -1166,7 +1186,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>68</v>
       </c>
@@ -1180,7 +1200,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -1194,7 +1214,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>13</v>
       </c>
@@ -1208,7 +1228,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>13</v>
       </c>
@@ -1222,7 +1242,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -1236,7 +1256,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -1250,7 +1270,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>13</v>
       </c>
@@ -1264,7 +1284,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>24</v>
       </c>
@@ -1278,7 +1298,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -1294,6 +1314,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>